--- a/single_mabs/4PL_plate_fit/v2/model_tracker.xlsx
+++ b/single_mabs/4PL_plate_fit/v2/model_tracker.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaddock\repos\titration_pnlme\single_mabs\4PL_plate_fit\v2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDB8ECE2-2398-4BE0-BC3C-BB9BABBF20B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8EB9D5C3-5E08-4CF6-BBA8-6C7262F76D5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-26730" yWindow="3060" windowWidth="21600" windowHeight="11265" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="29">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="330" uniqueCount="30">
   <si>
     <t>m0</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>m11</t>
+  </si>
+  <si>
+    <t>m16</t>
   </si>
 </sst>
 </file>
@@ -540,6 +543,9 @@
       <c r="R1" t="s">
         <v>14</v>
       </c>
+      <c r="S1" t="s">
+        <v>29</v>
+      </c>
     </row>
     <row r="2" spans="1:126" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -601,7 +607,9 @@
       <c r="R3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S3"/>
+      <c r="S3" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="T3"/>
       <c r="U3"/>
       <c r="V3"/>
@@ -762,6 +770,9 @@
       <c r="R4" t="s">
         <v>18</v>
       </c>
+      <c r="S4" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="5" spans="1:126" x14ac:dyDescent="0.25">
       <c r="B5" t="s">
@@ -815,6 +826,9 @@
       <c r="R5" t="s">
         <v>18</v>
       </c>
+      <c r="S5" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="6" spans="1:126" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
@@ -868,6 +882,9 @@
       <c r="R6" t="s">
         <v>17</v>
       </c>
+      <c r="S6" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="7" spans="1:126" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
@@ -924,7 +941,9 @@
       <c r="R7" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S7"/>
+      <c r="S7" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="T7"/>
       <c r="U7"/>
       <c r="V7"/>
@@ -1085,6 +1104,9 @@
       <c r="R8" t="s">
         <v>17</v>
       </c>
+      <c r="S8" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="9" spans="1:126" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
@@ -1138,6 +1160,9 @@
       <c r="R9" t="s">
         <v>17</v>
       </c>
+      <c r="S9" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:126" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
@@ -1194,7 +1219,9 @@
       <c r="R10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S10"/>
+      <c r="S10" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="T10"/>
       <c r="U10"/>
       <c r="V10"/>
@@ -1355,6 +1382,9 @@
       <c r="R11" t="s">
         <v>18</v>
       </c>
+      <c r="S11" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="12" spans="1:126" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
@@ -1408,6 +1438,9 @@
       <c r="R12" t="s">
         <v>18</v>
       </c>
+      <c r="S12" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:126" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
@@ -1464,7 +1497,9 @@
       <c r="R13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="S13"/>
+      <c r="S13" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="T13"/>
       <c r="U13"/>
       <c r="V13"/>
@@ -1625,6 +1660,9 @@
       <c r="R14" t="s">
         <v>17</v>
       </c>
+      <c r="S14" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="15" spans="1:126" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
@@ -1678,6 +1716,9 @@
       <c r="R15" t="s">
         <v>18</v>
       </c>
+      <c r="S15" s="1" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="16" spans="1:126" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
@@ -1734,7 +1775,9 @@
       <c r="R16" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S16"/>
+      <c r="S16" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
@@ -1895,6 +1938,9 @@
       <c r="R17" t="s">
         <v>17</v>
       </c>
+      <c r="S17" t="s">
+        <v>17</v>
+      </c>
     </row>
     <row r="18" spans="1:126" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
@@ -1951,7 +1997,9 @@
       <c r="R18" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="S18"/>
+      <c r="S18" s="1" t="s">
+        <v>18</v>
+      </c>
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
@@ -2112,6 +2160,9 @@
       <c r="R19" t="s">
         <v>17</v>
       </c>
+      <c r="S19" t="s">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
